--- a/docs/StructureDefinition-HAHConsent.xlsx
+++ b/docs/StructureDefinition-HAHConsent.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="372">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T17:33:17+08:00</t>
+    <t>2026-09-29T04:34:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>記錄照護同意的狀態、範圍、時間及來源文件。此資源不取代可執行的醫囑，也不以一般同意代替 DNR 決定。</t>
+    <t>記錄照護同意的狀態、範圍、時間及來源文件。</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1069,10 +1069,7 @@
     <t>When the purpose of use tag is on the data, access request purpose of use shall not conflict.</t>
   </si>
   <si>
-    <t>What purposes of use are controlled by this exception. If more than one label is specified, operations must have all the specified labels.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-PurposeOfUse|3.1.0</t>
   </si>
   <si>
     <t>Consent.provision.class</t>
@@ -1498,17 +1495,17 @@
   <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="34.33203125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.33203125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="33.671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.8671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="117.01953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="114.76171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1517,26 +1514,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="47.265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="107.984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.0703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="47.2265625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="69.27734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.796875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="28.8359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="39.8203125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="25.59375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="38.8984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="24.74609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="28.5078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7288,11 +7285,9 @@
       <c r="X51" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y51" t="s" s="2">
+      <c r="Y51" s="2"/>
+      <c r="Z51" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7339,10 +7334,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7368,13 +7363,13 @@
         <v>326</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7403,11 +7398,11 @@
         <v>178</v>
       </c>
       <c r="Y52" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="Z52" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="Z52" t="s" s="2">
-        <v>343</v>
-      </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
       </c>
@@ -7424,7 +7419,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7453,10 +7448,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7482,13 +7477,13 @@
         <v>175</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7517,11 +7512,11 @@
         <v>322</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
       </c>
@@ -7538,7 +7533,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7567,10 +7562,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7596,13 +7591,13 @@
         <v>298</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7652,7 +7647,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7681,10 +7676,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7710,10 +7705,10 @@
         <v>237</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7721,7 +7716,7 @@
         <v>20</v>
       </c>
       <c r="Q55" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R55" t="s" s="2">
         <v>20</v>
@@ -7766,7 +7761,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -7795,10 +7790,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7907,10 +7902,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8021,10 +8016,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8137,10 +8132,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8166,10 +8161,10 @@
         <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8199,11 +8194,11 @@
         <v>167</v>
       </c>
       <c r="Y59" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="Z59" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="Z59" t="s" s="2">
-        <v>365</v>
-      </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
       </c>
@@ -8220,7 +8215,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>88</v>
@@ -8249,10 +8244,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8275,13 +8270,13 @@
         <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8332,7 +8327,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>88</v>
@@ -8361,10 +8356,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8390,10 +8385,10 @@
         <v>79</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8444,7 +8439,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
